--- a/assets/docs/lop5/Lich su va Dia li - Lop 5.xlsx
+++ b/assets/docs/lop5/Lich su va Dia li - Lop 5.xlsx
@@ -1253,11 +1253,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS xem hiện vật, di tích liên quan “Triều lý và việc định đô ở thăng long” qua bảo tàng số.</t>
-        </is>
-      </c>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1349,11 +1345,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>NLS-ST (Cơ bản 2): HS dùng công cụ trên máy dựng trục thời gian, sắp các sự kiện của bài theo đúng thứ tự.</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1505,11 +1497,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS xem hiện vật, di tích liên quan “Khởi nghĩa lam sơn và triều hậu lê” qua bảo tàng số.</t>
-        </is>
-      </c>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1601,11 +1589,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>NLS-ST (Cơ bản 2): HS dùng công cụ trên máy dựng trục thời gian, sắp các sự kiện của bài theo đúng thứ tự.</t>
-        </is>
-      </c>
+      <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2279,11 +2263,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Dùng quả địa cầu số hoặc bản đồ thế giới tương tác.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
